--- a/data/trans_orig/IP16A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1520</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>23161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27945</t>
+          <t>28017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>25999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>51443</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57404</t>
+          <t>57170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>623</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10438</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>37612</t>
+          <t>37852</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42601</t>
+          <t>42598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40522</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47666</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81066</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89891</t>
+          <t>89530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,06%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20333</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42231</t>
+          <t>42448</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>528</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>719</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>2110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9151</t>
+          <t>9460</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>25666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30015</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>32670</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60830</t>
+          <t>60521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67993</t>
+          <t>67871</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,98%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6322</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>17167</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12127</t>
+          <t>11788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24861</t>
+          <t>25026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>113010</t>
+          <t>112934</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121618</t>
+          <t>121263</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127277</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137834</t>
+          <t>137597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244363</t>
+          <t>244198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257097</t>
+          <t>257436</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,62%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10338</t>
+          <t>10314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,77%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32489</t>
+          <t>32794</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36472</t>
+          <t>36411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64585</t>
+          <t>64609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72379</t>
+          <t>72889</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>5935</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>502</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47893</t>
+          <t>47750</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>53047</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115063</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119802</t>
+          <t>119940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,58%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>714</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4664</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1417</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8165</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23125</t>
+          <t>23315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23251</t>
+          <t>23245</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49620</t>
+          <t>49722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56397</t>
+          <t>56368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23741</t>
+          <t>24079</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>21561</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>47636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11738</t>
+          <t>11430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12296</t>
+          <t>11872</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19215</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135483</t>
+          <t>135791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>143917</t>
+          <t>143741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>145670</t>
+          <t>146094</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155281</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285972</t>
+          <t>285950</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297460</t>
+          <t>297912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,62%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5014</t>
+          <t>5079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24217</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18962</t>
+          <t>18897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>23369</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44942</t>
+          <t>44812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50080</t>
+          <t>50074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>6979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>38655</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37256</t>
+          <t>36994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42438</t>
+          <t>42414</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,7 +5153,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78518</t>
+          <t>78356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>30394</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66560</t>
+          <t>66518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17996</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>38940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>44235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14984</t>
+          <t>14087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>121790</t>
+          <t>121728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126765</t>
+          <t>126768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>112001</t>
+          <t>111647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>120221</t>
+          <t>120071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235753</t>
+          <t>236650</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245858</t>
+          <t>246001</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>876</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,49%</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12780</t>
+          <t>12837</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16539</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>31251</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37529</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1578</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6992,7 +6992,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42964</t>
+          <t>43830</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,7 +7065,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>47406</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92951</t>
+          <t>92802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32557</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>41529</t>
+          <t>42032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76958</t>
+          <t>76294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1201</t>
+          <t>974</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9958</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72651</t>
+          <t>73438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57356</t>
+          <t>57200</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>63905</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132691</t>
+          <t>134405</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141448</t>
+          <t>141675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>818</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7380</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170335</t>
+          <t>169891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176942</t>
+          <t>176897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170272</t>
+          <t>170673</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179244</t>
+          <t>179214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>345182</t>
+          <t>344235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355068</t>
+          <t>355181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP16A03-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3617</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2796</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5874</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6451</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,63%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3656</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1520</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26038</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>87,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26239</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23161</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28017</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>22584</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>27974</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,37%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>79,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>28929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>25999</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51443</t>
+          <t>51540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57170</t>
+          <t>57446</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29655</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>29035</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>29655</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6185</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11155</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2040</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>623</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5369</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5388</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,42%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6185</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2873</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11045</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,14%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44775</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>47702</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>87,86%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>41181</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>37852</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>42598</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>37833</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>42606</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,58%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>44775</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>39915</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48087</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>87,86%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80826</t>
+          <t>81039</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>89530</t>
+          <t>89404</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>50960</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>43221</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>50960</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,102 +1414,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4133</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3170</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3869</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,79%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>17,19%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3414</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3925</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23171</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>19733</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>82,68%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>21879</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>19337</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,21%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>82,81%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23171</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>20452</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,09%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>67</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>42448</t>
+          <t>42265</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23866</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>22507</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>23866</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2858</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6659</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>16,88%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1811</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4877</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>523</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4828</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2858</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6768</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9460</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>36580</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32779</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38717</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>83,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>28732</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>25666</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30017</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>25715</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>30020</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>94,07%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,28%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>36580</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>32670</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>38570</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,75%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60521</t>
+          <t>60783</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67871</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>39438</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>30543</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10465</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16150</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>7275</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4042</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12371</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3898</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>12252</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,81%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10465</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>6322</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>17167</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11887</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25026</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>133454</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>127769</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>137481</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>92,73%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>118030</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>112934</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>121263</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>113053</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>121407</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,19%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,13%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>96,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>133454</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>126752</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>137597</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>92,73%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>244198</t>
+          <t>243989</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>257436</t>
+          <t>257337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,58%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>143919</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>125305</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>143919</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4576</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1964</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9298</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3703</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3616</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>4576</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9005</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>5,24%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10314</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>33850</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>29128</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>36462</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>88,09%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,8%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>35766</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32794</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>32881</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,85%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,09%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>33850</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>29421</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>36411</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>88,09%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>76,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>94,76%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>102</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64609</t>
+          <t>64606</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72889</t>
+          <t>72814</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2883,7 +2883,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>38426</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>55</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>36497</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>38426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2311</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>638</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5935</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5651</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>51374</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>47750</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>53047</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>48034</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>53028</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,69%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114813</t>
+          <t>114767</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>119940</t>
+          <t>119781</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>66757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53685</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>66757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3632</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>13,01%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2844</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>714</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6555</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>9,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>21,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>887</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4670</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3474,67 +3474,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>27028</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24283</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>86,99%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>27026</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23315</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>29156</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>24069</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>29160</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>90,48%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>78,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>27028</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>23245</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>96,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49722</t>
+          <t>49208</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>56368</t>
+          <t>56383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27915</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>29870</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>27915</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3704,102 +3704,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2485</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>678</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3090</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3285</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>11,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1285</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4401</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24261</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22383</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>26491</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24079</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>23884</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>87,91%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>24261</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>21561</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>86,7%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>73</t>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47636</t>
+          <t>47438</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>27169</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>24868</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6070</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11462</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>6564</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11430</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3342</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>11801</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6070</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11872</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7275</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>151896</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>146504</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>155326</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,74%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>140657</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>135791</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>143741</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>135420</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>143879</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,54%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>92,24%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>151896</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>146094</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>155050</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285950</t>
+          <t>286011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>297912</t>
+          <t>297183</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>157966</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>212</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>147221</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>157966</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1928</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5112</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>910</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2873</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5079</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>935</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -4730,74 +4730,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22048</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18864</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23396</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>26123</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>24160</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23732</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>87,79%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22048</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>18897</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23369</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>78,81%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>49946</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>23976</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>27033</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>23976</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5964</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>705</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3684</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3877</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6102</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6979</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -5073,74 +5073,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40887</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37132</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42406</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,87%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>41534</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>38555</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38362</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,82%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>40887</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>36994</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42414</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>124</t>
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78356</t>
+          <t>77994</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84626</t>
+          <t>84619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>43096</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>42239</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>43096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,107 +5303,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>593</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2626</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>593</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3052</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>2940</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>593</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3052</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5416,74 +5416,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>32853</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30820</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32853</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30394</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>98</t>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66518</t>
+          <t>66630</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>33446</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>36124</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1479</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5239</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,02%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>765</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3520</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1479</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,5%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21279</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17519</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>76,98%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>21300</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>18545</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>18346</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>83,15%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>21279</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>17814</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,5%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>78,27%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>59</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44235</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -5877,52 +5877,52 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22758</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>22065</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>22758</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3098</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11480</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,04%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>2380</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>693</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5733</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>706</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5554</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11629</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14087</t>
+          <t>14236</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>117066</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>111796</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>120178</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,96%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>90,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>125081</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>121728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>126768</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>121907</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>126755</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,13%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,5%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>117066</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>111647</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>120071</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,96%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>236650</t>
+          <t>236501</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>246001</t>
+          <t>246375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>123276</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127461</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>123276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2820</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,04%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>16,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3607</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1932</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>396</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5548</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>1868</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>365</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16379</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14613</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17128</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>83,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,25%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15217</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12837</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>95,21%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>80,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>13355</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10562</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14169</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,25%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>74,54%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20425</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16809</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>21961</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>75,18%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,23%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>68</t>
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>29733</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37464</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17433</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>15983</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>14169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>422</t>
+          <t>270</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6922,92 +6922,92 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2032</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1578</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>2258</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40965</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>39896</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>46201</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>43830</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>40530</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>38864</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40896</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,1%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>48623</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>47406</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48984</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>145</t>
@@ -7095,27 +7095,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>94824</t>
+          <t>81494</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92802</t>
+          <t>79873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41235</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>46623</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>40896</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>95607</t>
+          <t>82131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>897</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>645</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1542</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43074</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39443</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>89,7%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36210</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>32696</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,01%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>37303</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>34607</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>37948</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,3%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>91,2%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>45306</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>42032</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>46169</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,13%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>91,04%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>107</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>81517</t>
+          <t>80377</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76294</t>
+          <t>76083</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43971</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>37151</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46169</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>83320</t>
+          <t>81919</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2948</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4519</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2925</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>787</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7492</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3714</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>59365</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>55012</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>61680</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>77189</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73438</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,2%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>49213</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46195</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>49980</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>61767</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>57200</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>63905</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>88,42%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>138956</t>
+          <t>108579</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>134405</t>
+          <t>104630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>141675</t>
+          <t>111008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>62313</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>49980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142649</t>
+          <t>112293</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2440</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10178</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,17%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7824</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>763</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11528</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15681</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>159783</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>154774</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>162512</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>174819</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>169891</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>176897</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>176120</t>
+          <t>140400</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>170673</t>
+          <t>136107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179214</t>
+          <t>142229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>350939</t>
+          <t>300183</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>344235</t>
+          <t>293932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>355181</t>
+          <t>303638</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>164952</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>177715</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182201</t>
+          <t>142992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>359916</t>
+          <t>307944</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
